--- a/Projects/Datasets for Excel/Datasets for excel/business_growth_data.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/business_growth_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/11. SAMM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A092DB75-D151-A846-A1C7-E44DC2832B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74142BB7-5471-4B8B-9851-CCDC9E7674D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-95" yWindow="0" windowWidth="13232" windowHeight="16397" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="21">
   <si>
     <t>Business Area</t>
   </si>
@@ -94,14 +116,17 @@
   <si>
     <t>Profit</t>
   </si>
+  <si>
+    <t>year</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -155,18 +180,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,18 +497,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L202"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -522,7 +549,7 @@
         <v>440.1346063077014</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -548,7 +575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -574,8 +601,15 @@
         <f>SUM(C2:C201)</f>
         <v>2028364.1972564629</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <f>SUMIF($A$2:$A$201,K4,C2:C201)</f>
+        <v>571940.59546133352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -601,8 +635,15 @@
         <f>SUM(D2:D201)</f>
         <v>974397.10328944284</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L6" si="0">SUMIF($A$2:$A$201,K5,C3:C202)</f>
+        <v>534490.39752493426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -628,8 +669,15 @@
         <f>SUM(F2:F201)</f>
         <v>97845.048042711525</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <f>SUMIF($A$2:$A$201,K6,$C$4:$C$203)</f>
+        <v>439290.48343433806</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -656,7 +704,7 @@
         <v>956122.04592430848</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -677,7 +725,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -696,8 +744,15 @@
       <c r="F9" s="4">
         <v>505.89255891816299</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <f>SUMIF($A$2:$A$201,K9,$F$2:$F$206)</f>
+        <v>27484.240729705412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -722,8 +777,15 @@
       <c r="I10" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ref="L10:L11" si="1">SUMIF($A$2:$A$201,K10,$F$2:$F$206)</f>
+        <v>24537.725930384404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -749,8 +811,15 @@
         <f>AVERAGE(C2:C201)</f>
         <v>10141.820986282315</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>21450.965320316343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -777,7 +846,7 @@
         <v>4871.9855164472137</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -803,8 +872,16 @@
         <f>AVERAGE(F2:F201)</f>
         <v>489.22524021355764</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K13" t="str" cm="1">
+        <f t="array" ref="K13:K16">_xlfn.UNIQUE(E2:E201)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="L13">
+        <f>SUMIF($E$2:$E$201,K13,$D$2:$D$201)</f>
+        <v>268740.25306048244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -823,8 +900,15 @@
       <c r="F14" s="4">
         <v>469.0885555228291</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K14" t="str">
+        <v>Books</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:L16" si="2">SUMIF($E$2:$E$201,K14,$D$2:$D$201)</f>
+        <v>288484.54192339571</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -849,8 +933,15 @@
       <c r="I15" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K15" t="str">
+        <v>Home &amp; Kitchen</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>224780.18247097792</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -876,8 +967,15 @@
         <f>MAX(C2:C201)</f>
         <v>14766.289549727881</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K16" t="str">
+        <v>Toys &amp; Games</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>192392.12583458639</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -904,7 +1002,7 @@
         <v>7303.9166976839424</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -931,7 +1029,7 @@
         <v>769.62240525635798</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -950,8 +1048,15 @@
       <c r="F19" s="4">
         <v>514.20618051872361</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <f>COUNTIF(E2:E201,K19)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -976,8 +1081,15 @@
       <c r="I20" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ref="L20:L22" si="3">COUNTIF(E3:E202,K20)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1003,8 +1115,15 @@
         <f>MIN(C2:C201)</f>
         <v>4894.0203683318423</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1149,15 @@
         <f>MIN(D2:D201)</f>
         <v>2227.4072435733501</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K22" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1058,7 +1184,7 @@
         <v>195.38569452000729</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1203,15 @@
       <c r="F24" s="4">
         <v>290.53969287938548</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" cm="1">
+        <f t="array" ref="L24">_xlfn.UNIQUE(YEAR(B2:B201))</f>
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1098,7 +1231,7 @@
         <v>512.37219142335061</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1118,7 +1251,7 @@
         <v>486.98930458062961</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1138,7 +1271,7 @@
         <v>509.39532293855689</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1158,7 +1291,7 @@
         <v>594.30460873225184</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1178,7 +1311,7 @@
         <v>226.03228328104441</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1198,7 +1331,7 @@
         <v>443.06879465298152</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1218,7 +1351,7 @@
         <v>526.99043549407611</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -1238,7 +1371,7 @@
         <v>453.31544539472372</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1258,7 +1391,7 @@
         <v>358.30938868737411</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1278,7 +1411,7 @@
         <v>586.8963486896796</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1431,7 @@
         <v>527.68719058461284</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1318,7 +1451,7 @@
         <v>402.88954295555152</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1338,7 +1471,7 @@
         <v>531.48172045158242</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1358,7 +1491,7 @@
         <v>582.15857120497958</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1378,7 +1511,7 @@
         <v>500.52926462993611</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1398,7 +1531,7 @@
         <v>580.05648034309968</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -1418,7 +1551,7 @@
         <v>507.82601751616608</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1438,7 +1571,7 @@
         <v>460.47710173456449</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1458,7 +1591,7 @@
         <v>384.05794836000871</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -1478,7 +1611,7 @@
         <v>491.40692330283872</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1498,7 +1631,7 @@
         <v>519.42929380457713</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -1518,7 +1651,7 @@
         <v>587.58327615873304</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1538,7 +1671,7 @@
         <v>488.48925315127741</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1558,7 +1691,7 @@
         <v>545.74156062209909</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1578,7 +1711,7 @@
         <v>403.53879862662723</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1598,7 +1731,7 @@
         <v>421.7370844172475</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1618,7 +1751,7 @@
         <v>488.96107009731122</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1638,7 +1771,7 @@
         <v>394.53715360149857</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1658,7 +1791,7 @@
         <v>582.02478373246811</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1678,7 +1811,7 @@
         <v>546.31303293186068</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1698,7 +1831,7 @@
         <v>527.90957643924537</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1718,7 +1851,7 @@
         <v>533.8904125215945</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1738,7 +1871,7 @@
         <v>702.10435614847972</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -1758,7 +1891,7 @@
         <v>453.11358120332051</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1778,7 +1911,7 @@
         <v>279.85587144994417</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1798,7 +1931,7 @@
         <v>519.93001968964654</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1818,7 +1951,7 @@
         <v>494.93964590383342</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -1838,7 +1971,7 @@
         <v>448.24809574895971</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1858,7 +1991,7 @@
         <v>402.117014064123</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -1878,7 +2011,7 @@
         <v>456.08104781978523</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -1898,7 +2031,7 @@
         <v>518.13384292178216</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -1918,7 +2051,7 @@
         <v>449.71832993574623</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -1938,7 +2071,7 @@
         <v>741.24536795437484</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -1958,7 +2091,7 @@
         <v>403.94956183668518</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -1978,7 +2111,7 @@
         <v>420.68826372923292</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -1998,7 +2131,7 @@
         <v>271.13799599854713</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2018,7 +2151,7 @@
         <v>525.14844150215367</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2038,7 +2171,7 @@
         <v>298.35933722002397</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2058,7 +2191,7 @@
         <v>446.05453666254988</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2078,7 +2211,7 @@
         <v>472.4329465439443</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2231,7 @@
         <v>429.02720341531119</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2118,7 +2251,7 @@
         <v>673.88726774545103</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -2138,7 +2271,7 @@
         <v>599.43943913154988</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2158,7 +2291,7 @@
         <v>631.9136876301576</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2178,7 +2311,7 @@
         <v>411.75811814500821</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2198,7 +2331,7 @@
         <v>612.85940645145683</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -2218,7 +2351,7 @@
         <v>549.60009463439621</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -2238,7 +2371,7 @@
         <v>577.14059486768451</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -2258,7 +2391,7 @@
         <v>602.94388287827667</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2278,7 +2411,7 @@
         <v>409.12367540409468</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2431,7 @@
         <v>457.56823790220977</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2318,7 +2451,7 @@
         <v>586.25960113284509</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -2338,7 +2471,7 @@
         <v>234.43809070250671</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2358,7 +2491,7 @@
         <v>651.33280825732049</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -2378,7 +2511,7 @@
         <v>555.31320642075843</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -2398,7 +2531,7 @@
         <v>495.42960393397652</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2551,7 @@
         <v>522.05076557571738</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -2438,7 +2571,7 @@
         <v>397.00647166910232</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2458,7 +2591,7 @@
         <v>465.00566354108952</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -2478,7 +2611,7 @@
         <v>610.02843382203741</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2498,7 +2631,7 @@
         <v>629.80219723262212</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -2518,7 +2651,7 @@
         <v>769.62240525635798</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -2538,7 +2671,7 @@
         <v>492.60753337195848</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -2558,7 +2691,7 @@
         <v>434.14470331949963</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2578,7 +2711,7 @@
         <v>448.57660340600108</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -2598,7 +2731,7 @@
         <v>398.19581247126348</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2618,7 +2751,7 @@
         <v>492.21452440591491</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2638,7 +2771,7 @@
         <v>538.27324300122677</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -2658,7 +2791,7 @@
         <v>496.57577194680459</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2678,7 +2811,7 @@
         <v>609.63468456657984</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2698,7 +2831,7 @@
         <v>476.57841986554632</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -2718,7 +2851,7 @@
         <v>465.25493475014372</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -2738,7 +2871,7 @@
         <v>441.87315231396752</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -2758,7 +2891,7 @@
         <v>336.73654737655039</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -2778,7 +2911,7 @@
         <v>343.22322756915457</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -2798,7 +2931,7 @@
         <v>382.08420693623123</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -2818,7 +2951,7 @@
         <v>630.14280716647613</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -2838,7 +2971,7 @@
         <v>589.52602728899296</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -2858,7 +2991,7 @@
         <v>637.49640663929904</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -2878,7 +3011,7 @@
         <v>366.77883454054978</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -2898,7 +3031,7 @@
         <v>303.13753102139799</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -2918,7 +3051,7 @@
         <v>433.99436798659173</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -2938,7 +3071,7 @@
         <v>517.58189532960284</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -2958,7 +3091,7 @@
         <v>549.86902749098272</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -2978,7 +3111,7 @@
         <v>604.79721559680524</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -2998,7 +3131,7 @@
         <v>528.42796708072149</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -3018,7 +3151,7 @@
         <v>674.26687806556311</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -3038,7 +3171,7 @@
         <v>477.73943190516798</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -3058,7 +3191,7 @@
         <v>408.69207819582039</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -3078,7 +3211,7 @@
         <v>331.87817845055667</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -3098,7 +3231,7 @@
         <v>411.10286419045502</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -3118,7 +3251,7 @@
         <v>524.21179609851231</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -3138,7 +3271,7 @@
         <v>411.12797426463692</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3158,7 +3291,7 @@
         <v>593.67424635352575</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -3178,7 +3311,7 @@
         <v>641.23277060374426</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3198,7 +3331,7 @@
         <v>263.04130947733972</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3218,7 +3351,7 @@
         <v>586.40523004976478</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -3238,7 +3371,7 @@
         <v>276.03959413382631</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -3258,7 +3391,7 @@
         <v>540.14990550902871</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3411,7 @@
         <v>622.48705641936601</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -3298,7 +3431,7 @@
         <v>506.48561063435761</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -3318,7 +3451,7 @@
         <v>372.03108267957612</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3471,7 @@
         <v>441.45687957222282</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3358,7 +3491,7 @@
         <v>473.83545542890988</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -3378,7 +3511,7 @@
         <v>481.77552162100568</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -3398,7 +3531,7 @@
         <v>479.71031592333333</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -3418,7 +3551,7 @@
         <v>489.01172206906858</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -3438,7 +3571,7 @@
         <v>521.3480048910169</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -3458,7 +3591,7 @@
         <v>379.14263462667788</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -3478,7 +3611,7 @@
         <v>475.79801701297811</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -3498,7 +3631,7 @@
         <v>651.82611703557052</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>7</v>
       </c>
@@ -3518,7 +3651,7 @@
         <v>461.53545768574821</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3538,7 +3671,7 @@
         <v>455.61639068448022</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -3558,7 +3691,7 @@
         <v>607.81973037142382</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -3578,7 +3711,7 @@
         <v>244.08153336559039</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3598,7 +3731,7 @@
         <v>618.13786012882861</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3618,7 +3751,7 @@
         <v>436.80962419948332</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -3638,7 +3771,7 @@
         <v>516.39285724525871</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -3658,7 +3791,7 @@
         <v>509.63213559211971</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -3678,7 +3811,7 @@
         <v>594.24681192203934</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -3698,7 +3831,7 @@
         <v>473.24052537646531</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -3718,7 +3851,7 @@
         <v>432.19742184355488</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -3738,7 +3871,7 @@
         <v>629.78457906510994</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>7</v>
       </c>
@@ -3758,7 +3891,7 @@
         <v>263.58261828588189</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -3778,7 +3911,7 @@
         <v>502.03341817052433</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -3798,7 +3931,7 @@
         <v>365.20745773708802</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3818,7 +3951,7 @@
         <v>423.84266117434407</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -3838,7 +3971,7 @@
         <v>701.12566814631373</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3858,7 +3991,7 @@
         <v>495.54045735441429</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -3878,7 +4011,7 @@
         <v>519.5069697151381</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -3898,7 +4031,7 @@
         <v>321.84371442944092</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -3918,7 +4051,7 @@
         <v>427.09553412053037</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>8</v>
       </c>
@@ -3938,7 +4071,7 @@
         <v>519.65574007287853</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -3958,7 +4091,7 @@
         <v>535.47576931132176</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -3978,7 +4111,7 @@
         <v>561.68865543932793</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -3998,7 +4131,7 @@
         <v>500.86278989175759</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4018,7 +4151,7 @@
         <v>552.70042084546594</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -4038,7 +4171,7 @@
         <v>545.3781912635684</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>8</v>
       </c>
@@ -4058,7 +4191,7 @@
         <v>317.02595889954682</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4078,7 +4211,7 @@
         <v>503.70057219101488</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -4098,7 +4231,7 @@
         <v>576.7902407732704</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4118,7 +4251,7 @@
         <v>558.98798207345192</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -4138,7 +4271,7 @@
         <v>463.61411900292097</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -4158,7 +4291,7 @@
         <v>419.43734924606321</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -4178,7 +4311,7 @@
         <v>388.16880756783678</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -4198,7 +4331,7 @@
         <v>486.89459884585881</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -4218,7 +4351,7 @@
         <v>613.30798795597218</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -4238,7 +4371,7 @@
         <v>304.81958985183979</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -4258,7 +4391,7 @@
         <v>434.0108270270502</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -4278,7 +4411,7 @@
         <v>386.01975445732262</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -4298,7 +4431,7 @@
         <v>578.49575212405</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -4318,7 +4451,7 @@
         <v>444.56903734286988</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -4338,7 +4471,7 @@
         <v>452.93623418452091</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -4358,7 +4491,7 @@
         <v>478.3050430063351</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -4378,7 +4511,7 @@
         <v>544.53932508947969</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -4398,7 +4531,7 @@
         <v>460.7611001850363</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -4418,7 +4551,7 @@
         <v>195.38569452000729</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -4438,7 +4571,7 @@
         <v>554.33118913875194</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -4458,7 +4591,7 @@
         <v>543.9042957672043</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -4478,7 +4611,7 @@
         <v>478.04589716687872</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -4498,7 +4631,7 @@
         <v>391.59633793280648</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4518,7 +4651,7 @@
         <v>535.17801106813579</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -4538,7 +4671,7 @@
         <v>537.92355335355865</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>7</v>
       </c>
@@ -4558,7 +4691,7 @@
         <v>452.99671172991248</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>8</v>
       </c>
@@ -4578,7 +4711,7 @@
         <v>478.32685294244612</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>8</v>
       </c>
@@ -4598,7 +4731,7 @@
         <v>406.98434974756788</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>7</v>
       </c>
@@ -4616,6 +4749,13 @@
       </c>
       <c r="F201" s="4">
         <v>482.14109079126712</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B202" s="7"/>
+      <c r="F202" s="4">
+        <f>SUM(F2:F201)</f>
+        <v>97845.048042711525</v>
       </c>
     </row>
   </sheetData>

--- a/Projects/Datasets for Excel/Datasets for excel/business_growth_data.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/business_growth_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74142BB7-5471-4B8B-9851-CCDC9E7674D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE29770D-8690-4D66-8305-DE1EED8492C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-95" yWindow="0" windowWidth="13232" windowHeight="16397" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12946" yWindow="0" windowWidth="13232" windowHeight="16397" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -497,19 +497,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.75" customWidth="1"/>
+    <col min="1" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="4" width="16.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,7 +528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -548,8 +547,12 @@
       <c r="F2" s="4">
         <v>440.1346063077014</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G2" t="str">
+        <f>IF(OR(A2="North America",A2="South America"),"American","Non-American")</f>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -568,14 +571,18 @@
       <c r="F3" s="4">
         <v>388.41030140396049</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G66" si="0">IF(OR(A3="North America",A3="South America"),"American","Non-American")</f>
+        <v>Non-American</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -594,22 +601,26 @@
       <c r="F4" s="4">
         <v>576.66631816450865</v>
       </c>
-      <c r="H4" t="s">
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J4" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="K4" s="6">
         <f>SUM(C2:C201)</f>
         <v>2028364.1972564629</v>
       </c>
-      <c r="K4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <f>SUMIF($A$2:$A$201,K4,C2:C201)</f>
+      <c r="M4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <f>SUMIF($A$2:$A$201,M4,C2:C201)</f>
         <v>571940.59546133352</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -628,22 +639,26 @@
       <c r="F5" s="4">
         <v>535.6292817472289</v>
       </c>
-      <c r="H5" t="s">
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J5" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="6">
+      <c r="K5" s="6">
         <f>SUM(D2:D201)</f>
         <v>974397.10328944284</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>7</v>
       </c>
-      <c r="L5">
-        <f t="shared" ref="L5:L6" si="0">SUMIF($A$2:$A$201,K5,C3:C202)</f>
+      <c r="N5">
+        <f t="shared" ref="N5" si="1">SUMIF($A$2:$A$201,M5,C3:C202)</f>
         <v>534490.39752493426</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -662,22 +677,26 @@
       <c r="F6" s="4">
         <v>323.14615493229689</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J6" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="6">
+      <c r="K6" s="6">
         <f>SUM(F2:F201)</f>
         <v>97845.048042711525</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>9</v>
       </c>
-      <c r="L6">
-        <f>SUMIF($A$2:$A$201,K6,$C$4:$C$203)</f>
+      <c r="N6">
+        <f>SUMIF($A$2:$A$201,M6,$C$4:$C$203)</f>
         <v>439290.48343433806</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -696,15 +715,19 @@
       <c r="F7" s="4">
         <v>535.54817927437693</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="6">
-        <f>I4-I6-I5</f>
+      <c r="K7" s="6">
+        <f>K4-K6-K5</f>
         <v>956122.04592430848</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -723,9 +746,13 @@
       <c r="F8" s="4">
         <v>581.45198224878663</v>
       </c>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -744,15 +771,19 @@
       <c r="F9" s="4">
         <v>505.89255891816299</v>
       </c>
-      <c r="K9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <f>SUMIF($A$2:$A$201,K9,$F$2:$F$206)</f>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="M9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9">
+        <f>SUMIF($A$2:$A$201,M9,$F$2:$F$206)</f>
         <v>27484.240729705412</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -771,21 +802,25 @@
       <c r="F10" s="4">
         <v>481.49463289906578</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>7</v>
       </c>
-      <c r="L10">
-        <f t="shared" ref="L10:L11" si="1">SUMIF($A$2:$A$201,K10,$F$2:$F$206)</f>
+      <c r="N10">
+        <f t="shared" ref="N10:N11" si="2">SUMIF($A$2:$A$201,M10,$F$2:$F$206)</f>
         <v>24537.725930384404</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -804,22 +839,26 @@
       <c r="F11" s="4">
         <v>419.23515123836438</v>
       </c>
-      <c r="H11" t="s">
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J11" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="6">
+      <c r="K11" s="6">
         <f>AVERAGE(C2:C201)</f>
         <v>10141.820986282315</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>9</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="1"/>
+      <c r="N11">
+        <f t="shared" si="2"/>
         <v>21450.965320316343</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -838,15 +877,19 @@
       <c r="F12" s="4">
         <v>355.34653004366118</v>
       </c>
-      <c r="H12" t="s">
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J12" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="6">
+      <c r="K12" s="6">
         <f>AVERAGE(D2:D201)</f>
         <v>4871.9855164472137</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -865,23 +908,27 @@
       <c r="F13" s="4">
         <v>580.02979493400278</v>
       </c>
-      <c r="H13" t="s">
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J13" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="6">
+      <c r="K13" s="6">
         <f>AVERAGE(F2:F201)</f>
         <v>489.22524021355764</v>
       </c>
-      <c r="K13" t="str" cm="1">
-        <f t="array" ref="K13:K16">_xlfn.UNIQUE(E2:E201)</f>
+      <c r="M13" t="str" cm="1">
+        <f t="array" ref="M13:M16">_xlfn.UNIQUE(E2:E201)</f>
         <v>Electronics</v>
       </c>
-      <c r="L13">
-        <f>SUMIF($E$2:$E$201,K13,$D$2:$D$201)</f>
+      <c r="N13">
+        <f>SUMIF($E$2:$E$201,M13,$D$2:$D$201)</f>
         <v>268740.25306048244</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -900,15 +947,19 @@
       <c r="F14" s="4">
         <v>469.0885555228291</v>
       </c>
-      <c r="K14" t="str">
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="M14" t="str">
         <v>Books</v>
       </c>
-      <c r="L14">
-        <f t="shared" ref="L14:L16" si="2">SUMIF($E$2:$E$201,K14,$D$2:$D$201)</f>
+      <c r="N14">
+        <f t="shared" ref="N14:N16" si="3">SUMIF($E$2:$E$201,M14,$D$2:$D$201)</f>
         <v>288484.54192339571</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -927,21 +978,25 @@
       <c r="F15" s="4">
         <v>476.65333384563081</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K15" t="str">
+      <c r="M15" t="str">
         <v>Home &amp; Kitchen</v>
       </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
+      <c r="N15">
+        <f t="shared" si="3"/>
         <v>224780.18247097792</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -960,22 +1015,26 @@
       <c r="F16" s="4">
         <v>673.27211869191331</v>
       </c>
-      <c r="H16" t="s">
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J16" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="6">
+      <c r="K16" s="6">
         <f>MAX(C2:C201)</f>
         <v>14766.289549727881</v>
       </c>
-      <c r="K16" t="str">
+      <c r="M16" t="str">
         <v>Toys &amp; Games</v>
       </c>
-      <c r="L16">
-        <f t="shared" si="2"/>
+      <c r="N16">
+        <f t="shared" si="3"/>
         <v>192392.12583458639</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -994,15 +1053,19 @@
       <c r="F17" s="4">
         <v>568.45011068591907</v>
       </c>
-      <c r="H17" t="s">
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J17" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="6">
+      <c r="K17" s="6">
         <f>MAX(D2:D201)</f>
         <v>7303.9166976839424</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1021,15 +1084,19 @@
       <c r="F18" s="4">
         <v>537.08250012811015</v>
       </c>
-      <c r="H18" t="s">
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J18" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="6">
+      <c r="K18" s="6">
         <f>MAX(F2:F201)</f>
         <v>769.62240525635798</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1048,15 +1115,19 @@
       <c r="F19" s="4">
         <v>514.20618051872361</v>
       </c>
-      <c r="K19" t="s">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <f>COUNTIF(E2:E201,K19)</f>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="M19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N19">
+        <f>COUNTIF(E2:E201,M19)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1075,21 +1146,25 @@
       <c r="F20" s="4">
         <v>651.99948607657734</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="K20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K20" t="s">
-        <v>11</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ref="L20:L22" si="3">COUNTIF(E3:E202,K20)</f>
+      <c r="M20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N20">
+        <f t="shared" ref="N20:N22" si="4">COUNTIF(E3:E202,M20)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1108,22 +1183,26 @@
       <c r="F21" s="4">
         <v>671.9589307416195</v>
       </c>
-      <c r="H21" t="s">
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J21" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="6">
+      <c r="K21" s="6">
         <f>MIN(C2:C201)</f>
         <v>4894.0203683318423</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>12</v>
       </c>
-      <c r="L21">
-        <f t="shared" si="3"/>
+      <c r="N21">
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1142,22 +1221,26 @@
       <c r="F22" s="4">
         <v>592.95051114795285</v>
       </c>
-      <c r="H22" t="s">
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J22" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="6">
+      <c r="K22" s="6">
         <f>MIN(D2:D201)</f>
         <v>2227.4072435733501</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>13</v>
       </c>
-      <c r="L22">
-        <f t="shared" si="3"/>
+      <c r="N22">
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1176,15 +1259,19 @@
       <c r="F23" s="4">
         <v>558.22245913979248</v>
       </c>
-      <c r="H23" t="s">
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J23" t="s">
         <v>5</v>
       </c>
-      <c r="I23" s="6">
+      <c r="K23" s="6">
         <f>MIN(F2:F201)</f>
         <v>195.38569452000729</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1203,15 +1290,19 @@
       <c r="F24" s="4">
         <v>290.53969287938548</v>
       </c>
-      <c r="K24" t="s">
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="M24" t="s">
         <v>20</v>
       </c>
-      <c r="L24" cm="1">
-        <f t="array" ref="L24">_xlfn.UNIQUE(YEAR(B2:B201))</f>
+      <c r="N24" cm="1">
+        <f t="array" ref="N24">_xlfn.UNIQUE(YEAR(B2:B201))</f>
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1230,8 +1321,16 @@
       <c r="F25" s="4">
         <v>512.37219142335061</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+      <c r="J25">
+        <f>COUNTIF(G2:G201,"American")</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1250,8 +1349,16 @@
       <c r="F26" s="4">
         <v>486.98930458062961</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G26" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+      <c r="J26">
+        <f>COUNTIF(G3:G202,"Non-American")</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1270,8 +1377,12 @@
       <c r="F27" s="4">
         <v>509.39532293855689</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1290,8 +1401,12 @@
       <c r="F28" s="4">
         <v>594.30460873225184</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1310,8 +1425,12 @@
       <c r="F29" s="4">
         <v>226.03228328104441</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1330,8 +1449,12 @@
       <c r="F30" s="4">
         <v>443.06879465298152</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1350,8 +1473,12 @@
       <c r="F31" s="4">
         <v>526.99043549407611</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -1370,8 +1497,12 @@
       <c r="F32" s="4">
         <v>453.31544539472372</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1390,8 +1521,12 @@
       <c r="F33" s="4">
         <v>358.30938868737411</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1410,8 +1545,12 @@
       <c r="F34" s="4">
         <v>586.8963486896796</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1430,8 +1569,12 @@
       <c r="F35" s="4">
         <v>527.68719058461284</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1450,8 +1593,12 @@
       <c r="F36" s="4">
         <v>402.88954295555152</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1470,8 +1617,12 @@
       <c r="F37" s="4">
         <v>531.48172045158242</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1490,8 +1641,12 @@
       <c r="F38" s="4">
         <v>582.15857120497958</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1510,8 +1665,12 @@
       <c r="F39" s="4">
         <v>500.52926462993611</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1530,8 +1689,12 @@
       <c r="F40" s="4">
         <v>580.05648034309968</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -1550,8 +1713,12 @@
       <c r="F41" s="4">
         <v>507.82601751616608</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1570,8 +1737,12 @@
       <c r="F42" s="4">
         <v>460.47710173456449</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1590,8 +1761,12 @@
       <c r="F43" s="4">
         <v>384.05794836000871</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -1610,8 +1785,12 @@
       <c r="F44" s="4">
         <v>491.40692330283872</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1630,8 +1809,12 @@
       <c r="F45" s="4">
         <v>519.42929380457713</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -1650,8 +1833,12 @@
       <c r="F46" s="4">
         <v>587.58327615873304</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1670,8 +1857,12 @@
       <c r="F47" s="4">
         <v>488.48925315127741</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1690,8 +1881,12 @@
       <c r="F48" s="4">
         <v>545.74156062209909</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1710,8 +1905,12 @@
       <c r="F49" s="4">
         <v>403.53879862662723</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1730,8 +1929,12 @@
       <c r="F50" s="4">
         <v>421.7370844172475</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1750,8 +1953,12 @@
       <c r="F51" s="4">
         <v>488.96107009731122</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1770,8 +1977,12 @@
       <c r="F52" s="4">
         <v>394.53715360149857</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1790,8 +2001,12 @@
       <c r="F53" s="4">
         <v>582.02478373246811</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1810,8 +2025,12 @@
       <c r="F54" s="4">
         <v>546.31303293186068</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1830,8 +2049,12 @@
       <c r="F55" s="4">
         <v>527.90957643924537</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1850,8 +2073,12 @@
       <c r="F56" s="4">
         <v>533.8904125215945</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1870,8 +2097,12 @@
       <c r="F57" s="4">
         <v>702.10435614847972</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -1890,8 +2121,12 @@
       <c r="F58" s="4">
         <v>453.11358120332051</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1910,8 +2145,12 @@
       <c r="F59" s="4">
         <v>279.85587144994417</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1930,8 +2169,12 @@
       <c r="F60" s="4">
         <v>519.93001968964654</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G60" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1950,8 +2193,12 @@
       <c r="F61" s="4">
         <v>494.93964590383342</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -1970,8 +2217,12 @@
       <c r="F62" s="4">
         <v>448.24809574895971</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1990,8 +2241,12 @@
       <c r="F63" s="4">
         <v>402.117014064123</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -2010,8 +2265,12 @@
       <c r="F64" s="4">
         <v>456.08104781978523</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64" t="str">
+        <f t="shared" si="0"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -2030,8 +2289,12 @@
       <c r="F65" s="4">
         <v>518.13384292178216</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -2050,8 +2313,12 @@
       <c r="F66" s="4">
         <v>449.71832993574623</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66" t="str">
+        <f t="shared" si="0"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2070,8 +2337,12 @@
       <c r="F67" s="4">
         <v>741.24536795437484</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67" t="str">
+        <f t="shared" ref="G67:G130" si="5">IF(OR(A67="North America",A67="South America"),"American","Non-American")</f>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -2090,8 +2361,12 @@
       <c r="F68" s="4">
         <v>403.94956183668518</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -2110,8 +2385,12 @@
       <c r="F69" s="4">
         <v>420.68826372923292</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2130,8 +2409,12 @@
       <c r="F70" s="4">
         <v>271.13799599854713</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2150,8 +2433,12 @@
       <c r="F71" s="4">
         <v>525.14844150215367</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G71" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2170,8 +2457,12 @@
       <c r="F72" s="4">
         <v>298.35933722002397</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2190,8 +2481,12 @@
       <c r="F73" s="4">
         <v>446.05453666254988</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -2210,8 +2505,12 @@
       <c r="F74" s="4">
         <v>472.4329465439443</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -2230,8 +2529,12 @@
       <c r="F75" s="4">
         <v>429.02720341531119</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2250,8 +2553,12 @@
       <c r="F76" s="4">
         <v>673.88726774545103</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -2270,8 +2577,12 @@
       <c r="F77" s="4">
         <v>599.43943913154988</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2290,8 +2601,12 @@
       <c r="F78" s="4">
         <v>631.9136876301576</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2310,8 +2625,12 @@
       <c r="F79" s="4">
         <v>411.75811814500821</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2330,8 +2649,12 @@
       <c r="F80" s="4">
         <v>612.85940645145683</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -2350,8 +2673,12 @@
       <c r="F81" s="4">
         <v>549.60009463439621</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -2370,8 +2697,12 @@
       <c r="F82" s="4">
         <v>577.14059486768451</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G82" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -2390,8 +2721,12 @@
       <c r="F83" s="4">
         <v>602.94388287827667</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2410,8 +2745,12 @@
       <c r="F84" s="4">
         <v>409.12367540409468</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2430,8 +2769,12 @@
       <c r="F85" s="4">
         <v>457.56823790220977</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2450,8 +2793,12 @@
       <c r="F86" s="4">
         <v>586.25960113284509</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -2470,8 +2817,12 @@
       <c r="F87" s="4">
         <v>234.43809070250671</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2490,8 +2841,12 @@
       <c r="F88" s="4">
         <v>651.33280825732049</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -2510,8 +2865,12 @@
       <c r="F89" s="4">
         <v>555.31320642075843</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -2530,8 +2889,12 @@
       <c r="F90" s="4">
         <v>495.42960393397652</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -2550,8 +2913,12 @@
       <c r="F91" s="4">
         <v>522.05076557571738</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -2570,8 +2937,12 @@
       <c r="F92" s="4">
         <v>397.00647166910232</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G92" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2590,8 +2961,12 @@
       <c r="F93" s="4">
         <v>465.00566354108952</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G93" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
@@ -2610,8 +2985,12 @@
       <c r="F94" s="4">
         <v>610.02843382203741</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2630,8 +3009,12 @@
       <c r="F95" s="4">
         <v>629.80219723262212</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
@@ -2650,8 +3033,12 @@
       <c r="F96" s="4">
         <v>769.62240525635798</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -2670,8 +3057,12 @@
       <c r="F97" s="4">
         <v>492.60753337195848</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -2690,8 +3081,12 @@
       <c r="F98" s="4">
         <v>434.14470331949963</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G98" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -2710,8 +3105,12 @@
       <c r="F99" s="4">
         <v>448.57660340600108</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G99" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -2730,8 +3129,12 @@
       <c r="F100" s="4">
         <v>398.19581247126348</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G100" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2750,8 +3153,12 @@
       <c r="F101" s="4">
         <v>492.21452440591491</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G101" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2770,8 +3177,12 @@
       <c r="F102" s="4">
         <v>538.27324300122677</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G102" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -2790,8 +3201,12 @@
       <c r="F103" s="4">
         <v>496.57577194680459</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G103" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2810,8 +3225,12 @@
       <c r="F104" s="4">
         <v>609.63468456657984</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G104" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2830,8 +3249,12 @@
       <c r="F105" s="4">
         <v>476.57841986554632</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G105" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -2850,8 +3273,12 @@
       <c r="F106" s="4">
         <v>465.25493475014372</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G106" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -2870,8 +3297,12 @@
       <c r="F107" s="4">
         <v>441.87315231396752</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G107" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -2890,8 +3321,12 @@
       <c r="F108" s="4">
         <v>336.73654737655039</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G108" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -2910,8 +3345,12 @@
       <c r="F109" s="4">
         <v>343.22322756915457</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G109" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -2930,8 +3369,12 @@
       <c r="F110" s="4">
         <v>382.08420693623123</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G110" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -2950,8 +3393,12 @@
       <c r="F111" s="4">
         <v>630.14280716647613</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G111" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -2970,8 +3417,12 @@
       <c r="F112" s="4">
         <v>589.52602728899296</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G112" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -2990,8 +3441,12 @@
       <c r="F113" s="4">
         <v>637.49640663929904</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G113" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -3010,8 +3465,12 @@
       <c r="F114" s="4">
         <v>366.77883454054978</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G114" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -3030,8 +3489,12 @@
       <c r="F115" s="4">
         <v>303.13753102139799</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G115" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -3050,8 +3513,12 @@
       <c r="F116" s="4">
         <v>433.99436798659173</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G116" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -3070,8 +3537,12 @@
       <c r="F117" s="4">
         <v>517.58189532960284</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G117" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -3090,8 +3561,12 @@
       <c r="F118" s="4">
         <v>549.86902749098272</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G118" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -3110,8 +3585,12 @@
       <c r="F119" s="4">
         <v>604.79721559680524</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G119" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3130,8 +3609,12 @@
       <c r="F120" s="4">
         <v>528.42796708072149</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G120" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -3150,8 +3633,12 @@
       <c r="F121" s="4">
         <v>674.26687806556311</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G121" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -3170,8 +3657,12 @@
       <c r="F122" s="4">
         <v>477.73943190516798</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -3190,8 +3681,12 @@
       <c r="F123" s="4">
         <v>408.69207819582039</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G123" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -3210,8 +3705,12 @@
       <c r="F124" s="4">
         <v>331.87817845055667</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -3230,8 +3729,12 @@
       <c r="F125" s="4">
         <v>411.10286419045502</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G125" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -3250,8 +3753,12 @@
       <c r="F126" s="4">
         <v>524.21179609851231</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G126" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -3270,8 +3777,12 @@
       <c r="F127" s="4">
         <v>411.12797426463692</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G127" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3290,8 +3801,12 @@
       <c r="F128" s="4">
         <v>593.67424635352575</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G128" t="str">
+        <f t="shared" si="5"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -3310,8 +3825,12 @@
       <c r="F129" s="4">
         <v>641.23277060374426</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G129" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3330,8 +3849,12 @@
       <c r="F130" s="4">
         <v>263.04130947733972</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G130" t="str">
+        <f t="shared" si="5"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -3350,8 +3873,12 @@
       <c r="F131" s="4">
         <v>586.40523004976478</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G131" t="str">
+        <f t="shared" ref="G131:G194" si="6">IF(OR(A131="North America",A131="South America"),"American","Non-American")</f>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -3370,8 +3897,12 @@
       <c r="F132" s="4">
         <v>276.03959413382631</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G132" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -3390,8 +3921,12 @@
       <c r="F133" s="4">
         <v>540.14990550902871</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G133" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -3410,8 +3945,12 @@
       <c r="F134" s="4">
         <v>622.48705641936601</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G134" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -3430,8 +3969,12 @@
       <c r="F135" s="4">
         <v>506.48561063435761</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G135" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -3450,8 +3993,12 @@
       <c r="F136" s="4">
         <v>372.03108267957612</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G136" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -3470,8 +4017,12 @@
       <c r="F137" s="4">
         <v>441.45687957222282</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G137" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3490,8 +4041,12 @@
       <c r="F138" s="4">
         <v>473.83545542890988</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G138" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -3510,8 +4065,12 @@
       <c r="F139" s="4">
         <v>481.77552162100568</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -3530,8 +4089,12 @@
       <c r="F140" s="4">
         <v>479.71031592333333</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G140" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -3550,8 +4113,12 @@
       <c r="F141" s="4">
         <v>489.01172206906858</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G141" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -3570,8 +4137,12 @@
       <c r="F142" s="4">
         <v>521.3480048910169</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G142" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -3590,8 +4161,12 @@
       <c r="F143" s="4">
         <v>379.14263462667788</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G143" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -3610,8 +4185,12 @@
       <c r="F144" s="4">
         <v>475.79801701297811</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G144" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -3630,8 +4209,12 @@
       <c r="F145" s="4">
         <v>651.82611703557052</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>7</v>
       </c>
@@ -3650,8 +4233,12 @@
       <c r="F146" s="4">
         <v>461.53545768574821</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G146" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -3670,8 +4257,12 @@
       <c r="F147" s="4">
         <v>455.61639068448022</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G147" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -3690,8 +4281,12 @@
       <c r="F148" s="4">
         <v>607.81973037142382</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G148" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -3710,8 +4305,12 @@
       <c r="F149" s="4">
         <v>244.08153336559039</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G149" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3730,8 +4329,12 @@
       <c r="F150" s="4">
         <v>618.13786012882861</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3750,8 +4353,12 @@
       <c r="F151" s="4">
         <v>436.80962419948332</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G151" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>7</v>
       </c>
@@ -3770,8 +4377,12 @@
       <c r="F152" s="4">
         <v>516.39285724525871</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G152" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -3790,8 +4401,12 @@
       <c r="F153" s="4">
         <v>509.63213559211971</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G153" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -3810,8 +4425,12 @@
       <c r="F154" s="4">
         <v>594.24681192203934</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G154" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -3830,8 +4449,12 @@
       <c r="F155" s="4">
         <v>473.24052537646531</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G155" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>7</v>
       </c>
@@ -3850,8 +4473,12 @@
       <c r="F156" s="4">
         <v>432.19742184355488</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G156" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -3870,8 +4497,12 @@
       <c r="F157" s="4">
         <v>629.78457906510994</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G157" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>7</v>
       </c>
@@ -3890,8 +4521,12 @@
       <c r="F158" s="4">
         <v>263.58261828588189</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G158" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -3910,8 +4545,12 @@
       <c r="F159" s="4">
         <v>502.03341817052433</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G159" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -3930,8 +4569,12 @@
       <c r="F160" s="4">
         <v>365.20745773708802</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G160" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3950,8 +4593,12 @@
       <c r="F161" s="4">
         <v>423.84266117434407</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G161" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -3970,8 +4617,12 @@
       <c r="F162" s="4">
         <v>701.12566814631373</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G162" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3990,8 +4641,12 @@
       <c r="F163" s="4">
         <v>495.54045735441429</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G163" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -4010,8 +4665,12 @@
       <c r="F164" s="4">
         <v>519.5069697151381</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G164" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -4030,8 +4689,12 @@
       <c r="F165" s="4">
         <v>321.84371442944092</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G165" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -4050,8 +4713,12 @@
       <c r="F166" s="4">
         <v>427.09553412053037</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G166" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>8</v>
       </c>
@@ -4070,8 +4737,12 @@
       <c r="F167" s="4">
         <v>519.65574007287853</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G167" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -4090,8 +4761,12 @@
       <c r="F168" s="4">
         <v>535.47576931132176</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G168" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -4110,8 +4785,12 @@
       <c r="F169" s="4">
         <v>561.68865543932793</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G169" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -4130,8 +4809,12 @@
       <c r="F170" s="4">
         <v>500.86278989175759</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G170" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -4150,8 +4833,12 @@
       <c r="F171" s="4">
         <v>552.70042084546594</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G171" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -4170,8 +4857,12 @@
       <c r="F172" s="4">
         <v>545.3781912635684</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G172" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>8</v>
       </c>
@@ -4190,8 +4881,12 @@
       <c r="F173" s="4">
         <v>317.02595889954682</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G173" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4210,8 +4905,12 @@
       <c r="F174" s="4">
         <v>503.70057219101488</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G174" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -4230,8 +4929,12 @@
       <c r="F175" s="4">
         <v>576.7902407732704</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G175" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4250,8 +4953,12 @@
       <c r="F176" s="4">
         <v>558.98798207345192</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G176" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -4270,8 +4977,12 @@
       <c r="F177" s="4">
         <v>463.61411900292097</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G177" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -4290,8 +5001,12 @@
       <c r="F178" s="4">
         <v>419.43734924606321</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G178" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -4310,8 +5025,12 @@
       <c r="F179" s="4">
         <v>388.16880756783678</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G179" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -4330,8 +5049,12 @@
       <c r="F180" s="4">
         <v>486.89459884585881</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G180" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -4350,8 +5073,12 @@
       <c r="F181" s="4">
         <v>613.30798795597218</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G181" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -4370,8 +5097,12 @@
       <c r="F182" s="4">
         <v>304.81958985183979</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G182" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -4390,8 +5121,12 @@
       <c r="F183" s="4">
         <v>434.0108270270502</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G183" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -4410,8 +5145,12 @@
       <c r="F184" s="4">
         <v>386.01975445732262</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G184" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -4430,8 +5169,12 @@
       <c r="F185" s="4">
         <v>578.49575212405</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G185" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -4450,8 +5193,12 @@
       <c r="F186" s="4">
         <v>444.56903734286988</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G186" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>7</v>
       </c>
@@ -4470,8 +5217,12 @@
       <c r="F187" s="4">
         <v>452.93623418452091</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G187" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -4490,8 +5241,12 @@
       <c r="F188" s="4">
         <v>478.3050430063351</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G188" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -4510,8 +5265,12 @@
       <c r="F189" s="4">
         <v>544.53932508947969</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G189" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -4530,8 +5289,12 @@
       <c r="F190" s="4">
         <v>460.7611001850363</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G190" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -4550,8 +5313,12 @@
       <c r="F191" s="4">
         <v>195.38569452000729</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G191" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -4570,8 +5337,12 @@
       <c r="F192" s="4">
         <v>554.33118913875194</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G192" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -4590,8 +5361,12 @@
       <c r="F193" s="4">
         <v>543.9042957672043</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G193" t="str">
+        <f t="shared" si="6"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -4610,8 +5385,12 @@
       <c r="F194" s="4">
         <v>478.04589716687872</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G194" t="str">
+        <f t="shared" si="6"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -4630,8 +5409,12 @@
       <c r="F195" s="4">
         <v>391.59633793280648</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G195" t="str">
+        <f t="shared" ref="G195:G201" si="7">IF(OR(A195="North America",A195="South America"),"American","Non-American")</f>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4650,8 +5433,12 @@
       <c r="F196" s="4">
         <v>535.17801106813579</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G196" t="str">
+        <f t="shared" si="7"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>7</v>
       </c>
@@ -4670,8 +5457,12 @@
       <c r="F197" s="4">
         <v>537.92355335355865</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G197" t="str">
+        <f t="shared" si="7"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>7</v>
       </c>
@@ -4690,8 +5481,12 @@
       <c r="F198" s="4">
         <v>452.99671172991248</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G198" t="str">
+        <f t="shared" si="7"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>8</v>
       </c>
@@ -4710,8 +5505,12 @@
       <c r="F199" s="4">
         <v>478.32685294244612</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G199" t="str">
+        <f t="shared" si="7"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>8</v>
       </c>
@@ -4730,8 +5529,12 @@
       <c r="F200" s="4">
         <v>406.98434974756788</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G200" t="str">
+        <f t="shared" si="7"/>
+        <v>American</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>7</v>
       </c>
@@ -4750,8 +5553,12 @@
       <c r="F201" s="4">
         <v>482.14109079126712</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G201" t="str">
+        <f t="shared" si="7"/>
+        <v>Non-American</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B202" s="7"/>
       <c r="F202" s="4">
         <f>SUM(F2:F201)</f>
